--- a/www/download/IND.gdp.s.du.rpO2.xlsx
+++ b/www/download/IND.gdp.s.du.rpO2.xlsx
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Reduction Problem: Ochoa 2</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -673,7 +678,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Austrália</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -683,84 +688,84 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>5243.40791191346</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>5282.49474263344</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>5535.45206761546</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>5366.52012549432</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>5161.41704725166</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>4030.50830991475</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>4359.39125049279</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>4228.06828113193</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>4831.38349100495</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>8321.26461059438</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>6063.359470127</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>6178.74938281843</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>7152.5372839947</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>8630.59013305473</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>10527.9517989542</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Áustria</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -770,84 +775,84 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>3067.94532311041</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>3184.40717594692</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>3064.53961762756</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>3029.23679406054</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>3022.50609431433</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>2522.51379845181</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>2418.5375159251</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>2637.69507407393</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>2770.29052200485</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>3070.80613343021</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>2758.62177717165</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>2853.64025217014</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>3638.23109845725</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>4027.61764979187</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>4934.0967404985</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Bélgica</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -857,84 +862,84 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>5036.57208691442</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>5254.26008620335</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>5269.66227376099</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>5138.72388796218</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>4882.84668751555</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>3876.31438703227</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>3669.58239685835</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>3776.29126574695</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>3809.06293815707</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>4113.96580465159</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>3984.87289531886</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>4283.12706154782</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>5561.72180935347</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>6319.45609393754</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>7198.60626791517</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Bulgaria</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -944,84 +949,84 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>3376.685990276</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>3819.49939869561</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>3812.88114585975</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>3040.97683587977</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>2653.95003864797</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>1953.43643306189</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>2032.52023210969</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>2084.57865666659</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>1964.74618072215</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>2086.59537548386</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>1906.18735312648</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>1889.9033573748</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>2586.83381629398</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>3147.00056277932</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>3495.11114256426</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Brasil</t>
+          <t>33</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1031,84 +1036,84 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0.171</t>
+          <t>170520.401771447</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>0.169</t>
+          <t>169417.751116076</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0.166</t>
+          <t>166046.856294793</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>0.158</t>
+          <t>157558.13645252</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>0.147</t>
+          <t>147475.015478143</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>0.109</t>
+          <t>109057.706360917</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>0.099</t>
+          <t>99122.4578153937</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>0.106</t>
+          <t>105801.735575603</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>0.102</t>
+          <t>101913.537610853</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>0.115</t>
+          <t>114504.872789571</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>109807.10625851</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>0.119</t>
+          <t>119238.661308329</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>0.194</t>
+          <t>194154.525557112</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>0.226</t>
+          <t>226312.36768349</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>0.268</t>
+          <t>267596.325879229</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Canadá</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1118,84 +1123,84 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0.015</t>
+          <t>14754.5546116611</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>0.015</t>
+          <t>14985.865970866</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>13488.4811910136</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>13348.4406642236</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>12515.7246802801</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>9258.1418190828</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>9306.51697560737</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>9721.3815665924</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>9888.81697378209</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>11314.2833294769</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>10335.8948238537</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>11788.5705289852</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>0.016</t>
+          <t>15650.6237616757</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>18322.1468945079</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>0.021</t>
+          <t>21268.8667057506</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>35</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1205,84 +1210,84 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2.693</t>
+          <t>2693404.99988095</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2.803</t>
+          <t>2802586.71169085</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2.48</t>
+          <t>2480136.47440919</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2.236</t>
+          <t>2236030.71375413</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>1.825</t>
+          <t>1824821.247058</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>1.462</t>
+          <t>1461859.35676462</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>1.594</t>
+          <t>1593699.49241325</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>1.785</t>
+          <t>1784969.10832345</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>2.032</t>
+          <t>2032264.44807571</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>2.524</t>
+          <t>2524246.33546023</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2.585</t>
+          <t>2585092.00966917</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>2.682</t>
+          <t>2682032.69238285</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>3.688</t>
+          <t>3687862.30099413</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>4.241</t>
+          <t>4241389.94069353</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>4.878</t>
+          <t>4878030.71895374</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Chipre</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1292,84 +1297,84 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>359.542807837716</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>359.186070455665</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>350.09537399122</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>335.423118808442</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>301.173811211695</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>224.047983027104</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>222.79227655593</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>246.478765421354</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>283.733799351288</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>326.04391081655</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>324.237224780382</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>382.0347548041</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>519.366856364062</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>594.284971714842</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>724.304321774357</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>República Tcheca</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1379,84 +1384,84 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>3908.80343635501</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>4113.39569625907</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>4005.92923784063</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>4043.69832442233</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>3711.23947335994</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>2934.17168842327</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>2593.31535999162</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>2648.0537675869</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>2796.34882400851</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>2999.40717550997</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>2909.35725957894</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>3141.97522792327</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>4103.6866657107</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>4933.51401078967</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>5343.01427839655</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Alemanha</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1466,84 +1471,84 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>0.027</t>
+          <t>26534.1978647483</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>0.027</t>
+          <t>27306.4999599439</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>0.026</t>
+          <t>26091.0827841854</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>0.026</t>
+          <t>25794.8842921092</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>0.023</t>
+          <t>23489.0114596395</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>18320.4535012703</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>0.017</t>
+          <t>17415.0103222315</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>18094.5996903362</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>18072.5374940342</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>20145.281319991</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>19229.2146994597</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>0.021</t>
+          <t>20504.896465104</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>0.026</t>
+          <t>26493.7869006621</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>30171.9260568974</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>0.034</t>
+          <t>33644.2511815306</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Dinamarca</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1553,84 +1558,84 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>1592.47672927853</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>1696.89961933412</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>1772.24900739836</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>2013.19528010808</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>1966.39165772062</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>1592.86748288294</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>1581.45166160118</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>1691.26202012543</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>1728.49696080776</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>1851.20866733458</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>1834.37443780109</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>2102.61348185028</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>2778.53045734769</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>2987.35654131626</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>3403.50279868531</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Espanha</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1640,84 +1645,84 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>12970.8696079193</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>13098.6162571172</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>12687.5084516614</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>12785.1491128032</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>12121.1794646945</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>9513.29630307978</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>9336.2753804303</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>10380.8404201742</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>11378.5104296435</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>12648.2729977447</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>12476.1574701457</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>13513.1705625308</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>0.017</t>
+          <t>17474.6442192948</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>19478.3932864181</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>0.021</t>
+          <t>20609.4058544414</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Estônia</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1727,84 +1732,84 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>2956.30689378601</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>3014.79145115924</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>5039.74779612831</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>5173.7681850601</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>493.376824038216</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>359.686838962459</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>505.492219594819</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>356.915950702188</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>332.295517107933</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>439.762004165395</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>575.147284248768</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>449.731753033594</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>573.486392242491</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>653.888723247742</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>546.568270789461</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Finlândia</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1814,84 +1819,84 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>2177.27566309348</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>2256.90067478336</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>2303.40342794476</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>2288.62849579757</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>2144.53012517621</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>1693.4641917484</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>1586.53182542222</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>1601.97345102907</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>1546.10860291589</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>1686.86469215357</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>1664.41884460281</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>1800.52094419855</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>2321.0192881196</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>2919.89855227252</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>2847.60575779248</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>França</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1901,84 +1906,84 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>12961.1535222419</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>13293.8534953523</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>13042.4180064322</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>13587.527599473</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>13095.4974730047</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>10119.7527572357</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>9480.40746883425</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>9678.19473433933</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>9747.59673956272</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>10381.4010310073</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>10084.3816713959</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>10689.2619016506</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>13696.8976130968</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>0.015</t>
+          <t>15179.3395180188</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>0.017</t>
+          <t>17041.6179019258</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Reino Unido</t>
+          <t>30</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1988,84 +1993,84 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>0.015</t>
+          <t>14668.2917128409</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>0.016</t>
+          <t>16252.5519749157</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>17835.4714708573</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>17665.2022160697</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>0.016</t>
+          <t>15739.6112292315</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>12063.4697857107</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>11160.3556434336</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>12109.9081731143</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>12332.2937669345</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>13860.6828807242</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>13847.3293545416</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>14307.5517874044</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>17506.4374617195</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>18411.0253094275</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>19065.6439900467</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Grécia</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2075,84 +2080,84 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>3983.48682549415</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>4126.56819191162</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>4499.5063138812</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>4469.70452151192</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>4014.36291494915</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>3062.57627712541</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>2493.52117191839</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>2629.95485824809</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>2664.844653657</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>3396.01133433825</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>2598.56678318696</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>3185.97613475307</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>3972.75336944352</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>4371.97233863899</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>5176.85836373567</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Hungria</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2162,84 +2167,84 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>3790.9062382782</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>3753.14387469955</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>4240.09854118204</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>4250.95770795523</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>3719.42739794834</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>3325.68595079009</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>2768.1752721036</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>3386.53255689521</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>3165.88881472601</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>3431.01708960094</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>3191.35670686644</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>3582.20292073249</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>4652.26494766225</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>4323.78803970704</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>4976.34138154476</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Indonésia</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2249,84 +2254,84 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>0.158</t>
+          <t>157545.83533559</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>0.183</t>
+          <t>183446.178473336</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>0.177</t>
+          <t>177325.391514955</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>0.178</t>
+          <t>178464.432411288</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>0.131</t>
+          <t>130952.889393141</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>99660.3980816314</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>0.078</t>
+          <t>77711.2435345609</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>0.084</t>
+          <t>83867.9999183971</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>0.088</t>
+          <t>87557.0347219462</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>0.098</t>
+          <t>98233.9079089808</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>0.079</t>
+          <t>78735.9634372982</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>0.069</t>
+          <t>69442.9453644375</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>0.092</t>
+          <t>91626.5595582567</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>0.102</t>
+          <t>102109.712622497</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>0.117</t>
+          <t>116811.384883624</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Índia</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2336,84 +2341,84 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>1.037</t>
+          <t>1036622.3634987</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>0.975</t>
+          <t>974576.872153927</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>0.876</t>
+          <t>876313.670300215</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>0.717</t>
+          <t>716582.912310152</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>0.602</t>
+          <t>602305.417231832</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>0.637</t>
+          <t>637304.116668888</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>0.767</t>
+          <t>766947.621717613</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>950424.787370672</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>1.14</t>
+          <t>1140466.76029517</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>1.449</t>
+          <t>1449207.93102449</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>1510362.2169139</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>1.618</t>
+          <t>1618453.07684764</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>2.097</t>
+          <t>2096720.10173001</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>2.45</t>
+          <t>2449528.15244136</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>2.981</t>
+          <t>2981436.79452353</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Irlanda</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2423,84 +2428,84 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>3097.79147668829</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>3280.75498638117</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>1730.88491107493</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>1968.71763961066</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>1940.28583747079</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>1784.13951551553</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>1679.74439916612</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>1709.08881654332</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>1684.38344538899</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>1651.83565110591</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>1557.91308258202</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>1685.40783100843</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>2205.99126143705</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>6365.3628317079</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>3153.76773499361</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Itália</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2510,84 +2515,84 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>30039.8749862978</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>0.033</t>
+          <t>33449.5554635883</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>0.033</t>
+          <t>32903.6458140131</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>0.032</t>
+          <t>32238.0041823097</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>30085.6080692081</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>0.025</t>
+          <t>24767.4251518196</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>0.023</t>
+          <t>22802.6268533756</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>0.025</t>
+          <t>24920.9809084757</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>0.029</t>
+          <t>29177.0915325779</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>0.029</t>
+          <t>29077.3521186006</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>0.028</t>
+          <t>27568.5705387019</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>0.029</t>
+          <t>29386.2712274622</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>0.036</t>
+          <t>35632.9965875862</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>0.038</t>
+          <t>38049.0561148099</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>0.041</t>
+          <t>40591.0186591148</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Japão</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2597,84 +2602,84 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>0.117</t>
+          <t>116526.967055454</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>0.108</t>
+          <t>107996.384959597</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>0.121</t>
+          <t>120903.325736376</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>0.117</t>
+          <t>117034.370937579</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>0.099</t>
+          <t>98636.9724517858</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>0.081</t>
+          <t>81070.1310495292</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>0.077</t>
+          <t>77299.8710637717</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>0.072</t>
+          <t>72301.5559551785</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>0.071</t>
+          <t>71046.9802507546</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>0.075</t>
+          <t>75390.2818790322</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>0.072</t>
+          <t>71557.039288017</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>0.075</t>
+          <t>75049.4011524677</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>0.097</t>
+          <t>96660.036937787</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>0.104</t>
+          <t>103958.213808808</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>110320.664026223</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Coreia do Sul</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2684,84 +2689,84 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>0.034</t>
+          <t>33764.9770221317</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>0.038</t>
+          <t>37734.7304861295</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>0.038</t>
+          <t>37894.3483705273</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>0.036</t>
+          <t>35661.7747081046</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>0.027</t>
+          <t>26771.8291296661</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>0.021</t>
+          <t>21301.6963837345</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>0.021</t>
+          <t>21140.8756372607</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>0.025</t>
+          <t>25064.6530823538</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>0.026</t>
+          <t>26002.0279199318</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>0.031</t>
+          <t>31340.6287311671</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>0.031</t>
+          <t>31150.2895791977</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>0.034</t>
+          <t>33989.1753437626</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>0.043</t>
+          <t>42968.3212073171</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>0.047</t>
+          <t>47050.606289625</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>0.056</t>
+          <t>55530.8029246762</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Lituânia</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2771,84 +2776,84 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>3145.33770115426</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>4339.4226638255</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>1230.18852930992</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>1326.5674676399</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>1262.68204401737</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>898.974102586013</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>712.045179294392</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>773.372368083253</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>850.642321272415</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>826.68782573984</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>901.381326265159</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>1076.77757611908</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>1252.23954052351</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>1317.93448523786</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>1539.15467189208</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Luxemburgo</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2858,84 +2863,84 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>283.294650088296</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>164.663599145164</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>146.053291689037</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>149.559536314398</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>144.005182411974</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>104.660474219366</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>92.0774148622098</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>102.710974788291</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>110.758946604041</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>129.201616480669</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>123.019908197281</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>133.659577873601</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>173.077507233041</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>205.362675168606</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>239.990077212671</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Letônia</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2945,84 +2950,84 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>909.886577555594</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>901.912704646098</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>776.915090139665</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>783.721002289328</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>724.049917333315</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>540.453399703551</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>442.204369611908</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>540.965429201914</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>775.166964009749</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>2514.79257573335</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>0.052</t>
+          <t>51961.8451490206</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>8150.34338826312</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>730.431032985724</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>792.871170552295</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>722.017580036988</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>México</t>
+          <t>40</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3032,84 +3037,84 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>0.073</t>
+          <t>73019.0625031976</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>0.078</t>
+          <t>77710.1741308994</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>0.078</t>
+          <t>77555.5912626574</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>79727.8604743956</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>0.077</t>
+          <t>77426.8907269344</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>0.065</t>
+          <t>64520.5727601084</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0.064</t>
+          <t>64426.7710790962</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>0.069</t>
+          <t>69295.6568687128</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>0.072</t>
+          <t>71667.7220655675</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>0.078</t>
+          <t>78022.1925167486</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>0.075</t>
+          <t>75342.0105718042</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>0.086</t>
+          <t>85611.0312819838</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>0.111</t>
+          <t>110666.731030153</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>0.132</t>
+          <t>132242.417175219</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>0.146</t>
+          <t>145788.991114001</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Malta</t>
+          <t>22</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3119,84 +3124,84 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>670.095580525825</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>685.566144631023</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>661.623197322073</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>660.013429463111</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>602.017022511818</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>439.540219390927</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>360.046405350247</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>448.931916281442</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>449.114484766017</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>478.596800838737</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>626.74665015986</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>530.953761994801</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>719.958427611294</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>848.73183213291</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>985.059577989296</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Países Baixos</t>
+          <t>23</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3206,84 +3211,84 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>4881.42250617066</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>4834.08029905555</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>4621.51447909365</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>4601.72701833535</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>4205.04088344809</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>3260.53808929179</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>2993.86319400834</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>2999.44790962037</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>3028.01475415559</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>3231.77504194887</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>3081.96666385426</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>3276.61497195233</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>4255.15563887743</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>4826.59739073063</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>5351.60030581122</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Polônia</t>
+          <t>24</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3293,84 +3298,84 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>0.023</t>
+          <t>22664.4786708184</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>0.021</t>
+          <t>21374.9754857526</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>0.021</t>
+          <t>20545.1076745729</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>0.021</t>
+          <t>21014.6190329546</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>0.021</t>
+          <t>20657.3440059529</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>12488.7722428034</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>12421.4467018458</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>13785.5341463664</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>13734.8773490957</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>0.015</t>
+          <t>14590.8290229159</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>0.016</t>
+          <t>16101.4513929743</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>0.016</t>
+          <t>16272.3366155638</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>19539.0911905519</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>0.022</t>
+          <t>21912.4343117647</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>0.026</t>
+          <t>25577.9815489854</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3380,84 +3385,84 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>4388.6954558344</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>4548.93639283446</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>4514.16107617449</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>4512.66192889931</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>4293.26328964303</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>3455.02743811955</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>3233.37595724233</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>3335.2778542619</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>3254.64416596283</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>3534.36405588791</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>3353.84301575745</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>3247.37018978545</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>3954.31402956373</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>4374.02186476752</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>4912.52390768276</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Romênia</t>
+          <t>26</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3467,84 +3472,84 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>0.033</t>
+          <t>33085.7056352908</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>30479.4324149989</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>30017.8441005977</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>0.029</t>
+          <t>28979.7836269114</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>0.027</t>
+          <t>27193.8871833323</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>0.021</t>
+          <t>20808.0128239549</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>0.024</t>
+          <t>24413.9155031066</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>0.025</t>
+          <t>25498.9447422462</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>0.027</t>
+          <t>26954.9536531642</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>0.027</t>
+          <t>26627.8447906736</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>0.024</t>
+          <t>23857.7821298952</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>0.027</t>
+          <t>27269.4535526695</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>10391.5880294811</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>12200.9399189914</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>0.015</t>
+          <t>14724.5106002167</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Rússia</t>
+          <t>43</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3554,84 +3559,84 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>0.188</t>
+          <t>187554.703145464</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>0.166</t>
+          <t>165903.395089881</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>0.139</t>
+          <t>138896.882194074</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>0.123</t>
+          <t>122842.98885533</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>0.104</t>
+          <t>103960.461352278</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>0.082</t>
+          <t>81920.7219559964</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>0.078</t>
+          <t>78215.4349310564</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>0.083</t>
+          <t>82541.0069531734</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>0.083</t>
+          <t>83442.1961815104</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>0.106</t>
+          <t>105547.885013972</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>0.114</t>
+          <t>114008.240973801</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>0.116</t>
+          <t>116136.942651798</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>0.139</t>
+          <t>138726.002247811</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>0.152</t>
+          <t>151887.220986837</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>0.156</t>
+          <t>156394.504127345</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Eslováquia</t>
+          <t>29</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3641,84 +3646,84 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>1460.50086472033</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>1601.20999357698</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>1451.4068692598</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>1273.56569521412</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>1202.79738430502</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>880.000708911798</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>861.833998899369</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>913.453980859004</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>905.433556882895</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>1029.75959095231</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>1026.83803123313</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>1130.65642371448</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>1404.44754660619</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>1934.4189169986</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>2200.93529108951</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Eslovênia</t>
+          <t>28</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3728,84 +3733,84 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>659.295973025958</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>700.26418929061</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>663.229451453408</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>659.481381228639</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>592.31121155754</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>463.92227905672</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>438.597103323731</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>464.94767585011</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>465.39128384113</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>501.009309545767</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>485.489057084283</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>521.191792591829</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>644.426503173849</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>777.300558956605</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>835.801391822921</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Suécia</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3815,84 +3820,84 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>2256.08460880917</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>2397.31155811727</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>2310.13173640003</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>2315.76029863903</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>2231.97209182412</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>1819.77879689236</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>1770.01878100646</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>1861.07185709197</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>1870.40896791332</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>2026.81082894799</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>1921.47637440721</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>2151.97528637797</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>2765.80313399939</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>3025.54678131941</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>3362.38904563394</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Turquia</t>
+          <t>42</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3902,84 +3907,84 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>39766.6092284488</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>0.041</t>
+          <t>41219.4624666432</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>0.047</t>
+          <t>47115.0829264794</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>0.048</t>
+          <t>48470.2975027989</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>0.043</t>
+          <t>42518.8317331655</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>0.061</t>
+          <t>60856.0310104834</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>0.074</t>
+          <t>74423.0415608006</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>0.186</t>
+          <t>186440.546620315</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>0.209</t>
+          <t>209483.866030246</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>0.229</t>
+          <t>228525.943597152</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>0.241</t>
+          <t>241324.81950089</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>0.256</t>
+          <t>256347.126998253</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>0.314</t>
+          <t>314476.846691416</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>0.371</t>
+          <t>371033.18748328</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>0.434</t>
+          <t>433605.347234815</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>China: Taiwan</t>
+          <t>36</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3989,84 +3994,84 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>11276.5006842359</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>10221.2631061874</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>9851.99794269159</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>9578.85224211528</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>8652.00406857869</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>6983.00879308644</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>6613.56400731105</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>6490.7699261011</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>6677.98121629081</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>7191.96549801333</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>7321.57696130247</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>8699.8076089221</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>12236.4803722528</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>0.015</t>
+          <t>14691.4086464809</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>0.016</t>
+          <t>16375.9478729838</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Estados Unidos</t>
+          <t>31</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4076,84 +4081,84 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>0.077</t>
+          <t>76876.5355347577</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>0.084</t>
+          <t>83812.3671336185</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>0.082</t>
+          <t>81840.9812952767</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>0.079</t>
+          <t>79238.6174069213</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>0.085</t>
+          <t>84972.5795965234</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>0.068</t>
+          <t>67535.3872431549</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>0.066</t>
+          <t>65936.207669003</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>70132.2472369459</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>0.076</t>
+          <t>76373.7706866904</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>0.073</t>
+          <t>72735.4631457644</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>0.071</t>
+          <t>71139.5348005733</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>0.078</t>
+          <t>78038.3947950893</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>0.093</t>
+          <t>92677.2086899351</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>0.103</t>
+          <t>102895.718212451</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>0.108</t>
+          <t>108051.825176377</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Resto do mundo</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4163,84 +4168,84 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>23.773</t>
+          <t>23772822.824387</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>24.016</t>
+          <t>24015636.6132016</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>24.595</t>
+          <t>24594722.2925739</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>25.089</t>
+          <t>25089083.4192327</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>26.011</t>
+          <t>26011169.7993639</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>26.13</t>
+          <t>26129614.4314201</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>25.844</t>
+          <t>25844252.2087612</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>26.452</t>
+          <t>26452193.9417241</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>29.393</t>
+          <t>29393484.802242</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>31.893</t>
+          <t>31892667.3801996</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>33.204</t>
+          <t>33203530.8921926</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>35.635</t>
+          <t>35635479.088783</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>39.185</t>
+          <t>39185068.542962</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>43.045</t>
+          <t>43044683.6617341</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>41.165</t>
+          <t>41164943.3306019</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Mundo</t>
+          <t>46</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4250,84 +4255,84 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>28.595</t>
+          <t>28594626.7219601</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>28.901</t>
+          <t>28900818.9245449</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>29.033</t>
+          <t>29033214.1277496</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>29.093</t>
+          <t>29093090.5956896</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>29.364</t>
+          <t>29363831.4480859</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>28.978</t>
+          <t>28978245.1912423</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>28.923</t>
+          <t>28922940.4630245</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>30.052</t>
+          <t>30052151.4673669</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>33.471</t>
+          <t>33470954.9644307</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>36.864</t>
+          <t>36863908.5153511</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>38.326</t>
+          <t>38325723.5015234</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>40.974</t>
+          <t>40974005.2832308</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>46.276</t>
+          <t>46276196.0003492</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>51.229</t>
+          <t>51228885.3853134</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>50.7</t>
+          <t>50699887.1344673</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Croácia</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4339,7 +4344,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Suíça</t>
+          <t>44</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4351,7 +4356,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Noruega</t>
+          <t>41</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4363,7 +4368,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Africa do Sul</t>
+          <t>45</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4375,7 +4380,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Resto do mundo - Asia</t>
+          <t>47</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4387,7 +4392,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Resto do mundo - America</t>
+          <t>50</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4399,7 +4404,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Resto do mundo - Europa</t>
+          <t>48</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4411,7 +4416,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Resto do mundo - Africa</t>
+          <t>49</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4423,7 +4428,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Resto do mundo - Oriente Medio</t>
+          <t>51</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4470,6 +4475,11 @@
           <t>gdp.s.du</t>
         </is>
       </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4504,6 +4514,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Reduction Problem: Ochoa 2</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>rpO2</t>
